--- a/docs/Villa_Somalia_SCADA_Device_and_IO_List_Rev1.xlsx
+++ b/docs/Villa_Somalia_SCADA_Device_and_IO_List_Rev1.xlsx
@@ -35900,7 +35900,7 @@
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="J140" s="11" t="inlineStr">
@@ -35957,7 +35957,7 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="J141" s="11" t="inlineStr">
@@ -47245,7 +47245,7 @@
     <row r="353">
       <c r="A353" s="11" t="inlineStr">
         <is>
-          <t>PRS-RLY-RLY-HEALTHY</t>
+          <t>PRS-RLY-HEALTHY</t>
         </is>
       </c>
       <c r="B353" s="11" t="inlineStr">
@@ -47669,7 +47669,7 @@
     <row r="361">
       <c r="A361" s="11" t="inlineStr">
         <is>
-          <t>PMS-RLY-RLY-HEALTHY</t>
+          <t>PMS-RLY-HEALTHY</t>
         </is>
       </c>
       <c r="B361" s="11" t="inlineStr">

--- a/docs/Villa_Somalia_SCADA_Device_and_IO_List_Rev1.xlsx
+++ b/docs/Villa_Somalia_SCADA_Device_and_IO_List_Rev1.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Device List'!$A$1:$N$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'IO List'!$A$1:$M$245</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Comms Points'!$A$1:$K$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Comms Point List'!$A$1:$K$457</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Comms Point List'!$A$1:$K$464</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Datasheets'!$A$1:$I$43</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -462,7 +462,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Siemens SICAM A8000 CP-8050 as plant controller and gateway. The embedded EMS keeps dispatch of PV, battery and generators.</t>
+          <t>Two Siemens SICAM A8000 CP-8050 in hot standby (A active, B standby) as plant controller and gateway. The embedded EMS keeps dispatch of PV, battery and generators.</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Siemens SICAM SCC on two servers (active and hot standby), linked to the CP-8050 by IEC 60870-5-104.</t>
+          <t>Siemens SICAM SCC on two servers (active and hot standby), linked to both controllers by IEC 60870-5-104.</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Totals: 244 hardwired signals and 456 communication points. Overall spare is 27%; row 5 drops to 19% (6 of 32 channels), just under the 20% target: add a third DI-8112 there if more yard signals appear.</t>
+          <t>Totals: 244 hardwired signals and 463 communication points. Overall spare is 27%; row 5 drops to 19% (6 of 32 channels), just under the 20% target: add a third DI-8112 there if more yard signals appear.</t>
         </is>
       </c>
     </row>
@@ -828,6 +828,16 @@
       <c r="B41" t="inlineStr">
         <is>
           <t>Comms Point List sheet added. Devices D49 and D50 added to the Device List.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Controller made redundant: two CP-8050 (A active, B hot standby), each with two power supplies, its own Ethernet interface, flash card and licences. I/O row 1 moved off the controller backplane onto its own CI-8532 so both controllers reach it. Communication points added for each controller's health and supplies, which controller is active, standby ready and switchover. Siemens to confirm the redundancy function, switchover time and how the I/O rows connect to both controllers.</t>
         </is>
       </c>
     </row>
@@ -2316,11 +2326,11 @@
         </is>
       </c>
       <c r="H23" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>11 kV switchroom</t>
+          <t>11 kV switchroom, SCADA cabinet</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -2345,7 +2355,7 @@
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>To SCADA servers A and B.</t>
+          <t>Hot standby pair (rev 1): controller A active, controller B standby, both on both core switches. Both connect to the SCADA servers by IEC 104. Siemens to confirm the redundancy function, switchover time and how the I/O rows connect to both controllers.</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2396,7 @@
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
@@ -2415,7 +2425,7 @@
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>Two for redundancy; confirm the CP-8050 supports a second supply.</t>
+          <t>Two per controller (rev 1). Confirm the CP-8050 supports a second supply.</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2466,7 @@
         </is>
       </c>
       <c r="H25" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
@@ -2485,7 +2495,7 @@
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>Not a managed switch.</t>
+          <t>Not a managed switch. One per controller (rev 1).</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2536,7 @@
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -2553,7 +2563,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N26" s="11" t="n"/>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>One per controller (rev 1).</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="25.5" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -2761,7 +2775,7 @@
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Alarm beacon and controller healthy output.</t>
+          <t>Alarm beacon and controller healthy output, driven by the active controller; the healthy output drops only if both controllers fail (rev 1).</t>
         </is>
       </c>
     </row>
@@ -2872,11 +2886,11 @@
         </is>
       </c>
       <c r="H31" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Rows 1, 2</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -2896,12 +2910,12 @@
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>Row 2</t>
+          <t>Rows 1, 2</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>24 V variant: CI-8530, 6MF2853-0AA00.</t>
+          <t>Row 1 moved off the controller backplane onto its own CI-8532 so both controllers reach it (rev 1). 24 V variant: CI-8530, 6MF2853-0AA00.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3026,7 @@
         </is>
       </c>
       <c r="H33" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -3039,7 +3053,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N33" s="11" t="n"/>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>One set per controller, including the redundancy function if licensed separately (rev 1).</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="38.25" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
@@ -20764,22 +20782,22 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>11 kV switchroom, beside the CP-8050</t>
+          <t>11 kV switchroom, SCADA cabinet</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>None (local row)</t>
+          <t>CI-8532 (electrical)</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6MF2853-2AA00</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>Backplane, no cable</t>
+          <t>Copper, inside the cabinet</t>
         </is>
       </c>
       <c r="F2" s="11" t="inlineStr">
@@ -21038,7 +21056,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Each remote row is a small panel near its equipment. Field contacts are wired a short distance to that panel; one link carries all signals to the CP-8050.</t>
+          <t>Each row has its own interface module and is reached by both controllers of the hot standby pair; only the active controller reads inputs and drives outputs. Each remote row is a small panel near its equipment, with field contacts wired a short distance to that panel.</t>
         </is>
       </c>
     </row>
@@ -21052,7 +21070,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Confirm with Siemens: fibre type and maximum length for CI-8533, and whether the remote link can share a fibre cable with the plant network on separate cores.</t>
+          <t>Confirm with Siemens: fibre type and maximum length for CI-8533, and whether the remote link can share a fibre cable with the plant network on separate cores. Also confirm how the I/O rows connect to both controllers of the redundant pair.</t>
         </is>
       </c>
     </row>
@@ -27919,7 +27937,7 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Controller healthy</t>
+          <t>Controller healthy (controllers A and B)</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
@@ -27938,7 +27956,7 @@
         </is>
       </c>
       <c r="G142" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" s="11" t="n">
         <v>1</v>
@@ -27952,7 +27970,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K142" s="11" t="n"/>
+      <c r="K142" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
@@ -27967,7 +27989,7 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Power supply 1 healthy</t>
+          <t>Power supply 1 healthy (controllers A and B)</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
@@ -27986,7 +28008,7 @@
         </is>
       </c>
       <c r="G143" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H143" s="11" t="n">
         <v>1</v>
@@ -28000,7 +28022,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K143" s="11" t="n"/>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
@@ -28015,7 +28041,7 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Power supply 2 healthy</t>
+          <t>Power supply 2 healthy (controllers A and B)</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
@@ -28034,7 +28060,7 @@
         </is>
       </c>
       <c r="G144" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H144" s="11" t="n">
         <v>1</v>
@@ -28048,7 +28074,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K144" s="11" t="n"/>
+      <c r="K144" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
@@ -28063,7 +28093,7 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>I/O row 1 healthy</t>
+          <t>I/O row 1 link healthy</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
@@ -28096,7 +28126,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K145" s="11" t="n"/>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Row 1 now has its own CI-8532 interface, so both controllers reach it</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="25.5" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
@@ -28386,51 +28420,204 @@
       </c>
       <c r="K151" s="11" t="n"/>
     </row>
-    <row r="152"/>
+    <row r="152">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>Controller active (controllers A and B)</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" s="11">
+        <f>G152*H152</f>
+        <v/>
+      </c>
+      <c r="J152" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Shows which controller is in control</t>
+        </is>
+      </c>
+    </row>
     <row r="153">
-      <c r="H153" s="2" t="inlineStr">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>Standby controller synchronised and ready</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="11">
+        <f>G153*H153</f>
+        <v/>
+      </c>
+      <c r="J153" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Off means a failure of the active controller would not be covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>Controller switchover occurred</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="11">
+        <f>G154*H154</f>
+        <v/>
+      </c>
+      <c r="J154" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Logged with time; resets on acknowledgement</t>
+        </is>
+      </c>
+    </row>
+    <row r="155"/>
+    <row r="156">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I153" s="2">
-        <f>SUM(I2:I151)</f>
+      <c r="I156" s="2">
+        <f>SUM(I2:I154)</f>
         <v/>
       </c>
     </row>
-    <row r="154">
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="I154" s="4">
-        <f>SUMIF(D2:D151,"Read",I2:I151)+SUMIF(D2:D151,"Read/Write",I2:I151)</f>
+    <row r="157">
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="I157" s="4">
+        <f>SUMIF(D2:D154,"Read",I2:I154)+SUMIF(D2:D154,"Read/Write",I2:I154)</f>
         <v/>
       </c>
     </row>
-    <row r="155">
-      <c r="H155" s="4" t="inlineStr">
+    <row r="158">
+      <c r="H158" s="4" t="inlineStr">
         <is>
           <t>Write</t>
         </is>
       </c>
-      <c r="I155" s="4">
-        <f>SUMIF(D2:D151,"Write",I2:I151)</f>
+      <c r="I158" s="4">
+        <f>SUMIF(D2:D154,"Write",I2:I154)</f>
         <v/>
       </c>
     </row>
-    <row r="156"/>
-    <row r="157">
-      <c r="A157" s="13" t="inlineStr">
+    <row r="159"/>
+    <row r="160">
+      <c r="A160" s="13" t="inlineStr">
         <is>
           <t>Typical points only. Replace each block with the vendor's point table when received.</t>
         </is>
       </c>
     </row>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
     <row r="161"/>
     <row r="162"/>
   </sheetData>
@@ -28446,7 +28633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K457"/>
+  <dimension ref="A1:K464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -51917,17 +52104,17 @@
     <row r="441">
       <c r="A441" s="11" t="inlineStr">
         <is>
-          <t>CP-HEALTHY</t>
+          <t>CP-A-HEALTHY</t>
         </is>
       </c>
       <c r="B441" s="11" t="inlineStr">
         <is>
-          <t>SICAM CP-8050 internal</t>
+          <t>SICAM CP-8050 A</t>
         </is>
       </c>
       <c r="C441" s="11" t="inlineStr">
         <is>
-          <t>Controller healthy</t>
+          <t>Controller A healthy</t>
         </is>
       </c>
       <c r="D441" s="11" t="inlineStr">
@@ -51965,22 +52152,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K441" s="11" t="n"/>
+      <c r="K441" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="11" t="inlineStr">
         <is>
-          <t>CP-PS1-OK</t>
+          <t>CP-A-PS1-OK</t>
         </is>
       </c>
       <c r="B442" s="11" t="inlineStr">
         <is>
-          <t>SICAM CP-8050 internal</t>
+          <t>SICAM CP-8050 A</t>
         </is>
       </c>
       <c r="C442" s="11" t="inlineStr">
         <is>
-          <t>Power supply 1 healthy</t>
+          <t>Controller A power supply 1 healthy</t>
         </is>
       </c>
       <c r="D442" s="11" t="inlineStr">
@@ -52018,22 +52209,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K442" s="11" t="n"/>
+      <c r="K442" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="11" t="inlineStr">
         <is>
-          <t>CP-PS2-OK</t>
+          <t>CP-A-PS2-OK</t>
         </is>
       </c>
       <c r="B443" s="11" t="inlineStr">
         <is>
-          <t>SICAM CP-8050 internal</t>
+          <t>SICAM CP-8050 A</t>
         </is>
       </c>
       <c r="C443" s="11" t="inlineStr">
         <is>
-          <t>Power supply 2 healthy</t>
+          <t>Controller A power supply 2 healthy</t>
         </is>
       </c>
       <c r="D443" s="11" t="inlineStr">
@@ -52071,22 +52266,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K443" s="11" t="n"/>
+      <c r="K443" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="11" t="inlineStr">
         <is>
-          <t>CP-ROW1-OK</t>
+          <t>CP-A-ACTIVE</t>
         </is>
       </c>
       <c r="B444" s="11" t="inlineStr">
         <is>
-          <t>SICAM CP-8050 internal</t>
+          <t>SICAM CP-8050 A</t>
         </is>
       </c>
       <c r="C444" s="11" t="inlineStr">
         <is>
-          <t>I/O row 1 healthy</t>
+          <t>Controller A active</t>
         </is>
       </c>
       <c r="D444" s="11" t="inlineStr">
@@ -52111,12 +52310,12 @@
       </c>
       <c r="H444" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I444" s="11" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J444" s="11" t="inlineStr">
@@ -52124,22 +52323,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K444" s="11" t="n"/>
+      <c r="K444" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Shows which controller is in control</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="11" t="inlineStr">
         <is>
-          <t>CP-ROW2-OK</t>
+          <t>CP-B-HEALTHY</t>
         </is>
       </c>
       <c r="B445" s="11" t="inlineStr">
         <is>
-          <t>SICAM CP-8050 internal</t>
+          <t>SICAM CP-8050 B</t>
         </is>
       </c>
       <c r="C445" s="11" t="inlineStr">
         <is>
-          <t>I/O row 2 link healthy</t>
+          <t>Controller B healthy</t>
         </is>
       </c>
       <c r="D445" s="11" t="inlineStr">
@@ -52177,22 +52380,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K445" s="11" t="n"/>
+      <c r="K445" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="11" t="inlineStr">
         <is>
-          <t>CP-ROW3-OK</t>
+          <t>CP-B-PS1-OK</t>
         </is>
       </c>
       <c r="B446" s="11" t="inlineStr">
         <is>
-          <t>SICAM CP-8050 internal</t>
+          <t>SICAM CP-8050 B</t>
         </is>
       </c>
       <c r="C446" s="11" t="inlineStr">
         <is>
-          <t>I/O row 3 link healthy</t>
+          <t>Controller B power supply 1 healthy</t>
         </is>
       </c>
       <c r="D446" s="11" t="inlineStr">
@@ -52230,22 +52437,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K446" s="11" t="n"/>
+      <c r="K446" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="11" t="inlineStr">
         <is>
-          <t>CP-ROW4-OK</t>
+          <t>CP-B-PS2-OK</t>
         </is>
       </c>
       <c r="B447" s="11" t="inlineStr">
         <is>
-          <t>SICAM CP-8050 internal</t>
+          <t>SICAM CP-8050 B</t>
         </is>
       </c>
       <c r="C447" s="11" t="inlineStr">
         <is>
-          <t>I/O row 4 link healthy</t>
+          <t>Controller B power supply 2 healthy</t>
         </is>
       </c>
       <c r="D447" s="11" t="inlineStr">
@@ -52283,22 +52494,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K447" s="11" t="n"/>
+      <c r="K447" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. One per controller of the hot standby pair</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="11" t="inlineStr">
         <is>
-          <t>CP-ROW5-OK</t>
+          <t>CP-B-ACTIVE</t>
         </is>
       </c>
       <c r="B448" s="11" t="inlineStr">
         <is>
-          <t>SICAM CP-8050 internal</t>
+          <t>SICAM CP-8050 B</t>
         </is>
       </c>
       <c r="C448" s="11" t="inlineStr">
         <is>
-          <t>I/O row 5 link healthy</t>
+          <t>Controller B active</t>
         </is>
       </c>
       <c r="D448" s="11" t="inlineStr">
@@ -52323,12 +52538,12 @@
       </c>
       <c r="H448" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I448" s="11" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J448" s="11" t="inlineStr">
@@ -52336,12 +52551,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K448" s="11" t="n"/>
+      <c r="K448" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Shows which controller is in control</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="11" t="inlineStr">
         <is>
-          <t>CP-ROW6-OK</t>
+          <t>CP-ROW1-OK</t>
         </is>
       </c>
       <c r="B449" s="11" t="inlineStr">
@@ -52351,7 +52570,7 @@
       </c>
       <c r="C449" s="11" t="inlineStr">
         <is>
-          <t>I/O row 6 link healthy</t>
+          <t>I/O row 1 link healthy</t>
         </is>
       </c>
       <c r="D449" s="11" t="inlineStr">
@@ -52389,12 +52608,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K449" s="11" t="n"/>
+      <c r="K449" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Row 1 now has its own CI-8532 interface, so both controllers reach it</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="11" t="inlineStr">
         <is>
-          <t>CP-LINK1-OK</t>
+          <t>CP-ROW2-OK</t>
         </is>
       </c>
       <c r="B450" s="11" t="inlineStr">
@@ -52404,7 +52627,7 @@
       </c>
       <c r="C450" s="11" t="inlineStr">
         <is>
-          <t>Link to each communication device healthy (8 links)</t>
+          <t>I/O row 2 link healthy</t>
         </is>
       </c>
       <c r="D450" s="11" t="inlineStr">
@@ -52447,7 +52670,7 @@
     <row r="451">
       <c r="A451" s="11" t="inlineStr">
         <is>
-          <t>CP-LINK2-OK</t>
+          <t>CP-ROW3-OK</t>
         </is>
       </c>
       <c r="B451" s="11" t="inlineStr">
@@ -52457,7 +52680,7 @@
       </c>
       <c r="C451" s="11" t="inlineStr">
         <is>
-          <t>Link to each communication device healthy (8 links)</t>
+          <t>I/O row 3 link healthy</t>
         </is>
       </c>
       <c r="D451" s="11" t="inlineStr">
@@ -52500,7 +52723,7 @@
     <row r="452">
       <c r="A452" s="11" t="inlineStr">
         <is>
-          <t>CP-LINK3-OK</t>
+          <t>CP-ROW4-OK</t>
         </is>
       </c>
       <c r="B452" s="11" t="inlineStr">
@@ -52510,7 +52733,7 @@
       </c>
       <c r="C452" s="11" t="inlineStr">
         <is>
-          <t>Link to each communication device healthy (8 links)</t>
+          <t>I/O row 4 link healthy</t>
         </is>
       </c>
       <c r="D452" s="11" t="inlineStr">
@@ -52553,7 +52776,7 @@
     <row r="453">
       <c r="A453" s="11" t="inlineStr">
         <is>
-          <t>CP-LINK4-OK</t>
+          <t>CP-ROW5-OK</t>
         </is>
       </c>
       <c r="B453" s="11" t="inlineStr">
@@ -52563,7 +52786,7 @@
       </c>
       <c r="C453" s="11" t="inlineStr">
         <is>
-          <t>Link to each communication device healthy (8 links)</t>
+          <t>I/O row 5 link healthy</t>
         </is>
       </c>
       <c r="D453" s="11" t="inlineStr">
@@ -52606,7 +52829,7 @@
     <row r="454">
       <c r="A454" s="11" t="inlineStr">
         <is>
-          <t>CP-LINK5-OK</t>
+          <t>CP-ROW6-OK</t>
         </is>
       </c>
       <c r="B454" s="11" t="inlineStr">
@@ -52616,7 +52839,7 @@
       </c>
       <c r="C454" s="11" t="inlineStr">
         <is>
-          <t>Link to each communication device healthy (8 links)</t>
+          <t>I/O row 6 link healthy</t>
         </is>
       </c>
       <c r="D454" s="11" t="inlineStr">
@@ -52659,7 +52882,7 @@
     <row r="455">
       <c r="A455" s="11" t="inlineStr">
         <is>
-          <t>CP-LINK6-OK</t>
+          <t>CP-LINK1-OK</t>
         </is>
       </c>
       <c r="B455" s="11" t="inlineStr">
@@ -52712,7 +52935,7 @@
     <row r="456">
       <c r="A456" s="11" t="inlineStr">
         <is>
-          <t>CP-LINK7-OK</t>
+          <t>CP-LINK2-OK</t>
         </is>
       </c>
       <c r="B456" s="11" t="inlineStr">
@@ -52765,58 +52988,437 @@
     <row r="457">
       <c r="A457" s="11" t="inlineStr">
         <is>
+          <t>CP-LINK3-OK</t>
+        </is>
+      </c>
+      <c r="B457" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="C457" s="11" t="inlineStr">
+        <is>
+          <t>Link to each communication device healthy (8 links)</t>
+        </is>
+      </c>
+      <c r="D457" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E457" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F457" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G457" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="H457" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I457" s="11" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="J457" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K457" s="11" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="11" t="inlineStr">
+        <is>
+          <t>CP-LINK4-OK</t>
+        </is>
+      </c>
+      <c r="B458" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="C458" s="11" t="inlineStr">
+        <is>
+          <t>Link to each communication device healthy (8 links)</t>
+        </is>
+      </c>
+      <c r="D458" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E458" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F458" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G458" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="H458" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I458" s="11" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="J458" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K458" s="11" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="11" t="inlineStr">
+        <is>
+          <t>CP-LINK5-OK</t>
+        </is>
+      </c>
+      <c r="B459" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="C459" s="11" t="inlineStr">
+        <is>
+          <t>Link to each communication device healthy (8 links)</t>
+        </is>
+      </c>
+      <c r="D459" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E459" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F459" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G459" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="H459" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I459" s="11" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="J459" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K459" s="11" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="11" t="inlineStr">
+        <is>
+          <t>CP-LINK6-OK</t>
+        </is>
+      </c>
+      <c r="B460" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="C460" s="11" t="inlineStr">
+        <is>
+          <t>Link to each communication device healthy (8 links)</t>
+        </is>
+      </c>
+      <c r="D460" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E460" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F460" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G460" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="H460" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I460" s="11" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="J460" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K460" s="11" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="11" t="inlineStr">
+        <is>
+          <t>CP-LINK7-OK</t>
+        </is>
+      </c>
+      <c r="B461" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="C461" s="11" t="inlineStr">
+        <is>
+          <t>Link to each communication device healthy (8 links)</t>
+        </is>
+      </c>
+      <c r="D461" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E461" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F461" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G461" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="H461" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I461" s="11" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="J461" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K461" s="11" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="11" t="inlineStr">
+        <is>
           <t>CP-LINK8-OK</t>
         </is>
       </c>
-      <c r="B457" s="11" t="inlineStr">
+      <c r="B462" s="11" t="inlineStr">
         <is>
           <t>SICAM CP-8050 internal</t>
         </is>
       </c>
-      <c r="C457" s="11" t="inlineStr">
+      <c r="C462" s="11" t="inlineStr">
         <is>
           <t>Link to each communication device healthy (8 links)</t>
         </is>
       </c>
-      <c r="D457" s="11" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="E457" s="11" t="inlineStr">
+      <c r="D462" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E462" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F457" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G457" s="11" t="inlineStr">
+      <c r="F462" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G462" s="11" t="inlineStr">
         <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="H457" s="11" t="inlineStr">
+      <c r="H462" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I457" s="11" t="inlineStr">
+      <c r="I462" s="11" t="inlineStr">
         <is>
           <t>Off</t>
         </is>
       </c>
-      <c r="J457" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K457" s="11" t="n"/>
+      <c r="J462" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K462" s="11" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="11" t="inlineStr">
+        <is>
+          <t>CP-REDUN-OK</t>
+        </is>
+      </c>
+      <c r="B463" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="C463" s="11" t="inlineStr">
+        <is>
+          <t>Standby controller synchronised and ready</t>
+        </is>
+      </c>
+      <c r="D463" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E463" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F463" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G463" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="H463" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I463" s="11" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="J463" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K463" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Off means a failure of the active controller would not be covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="11" t="inlineStr">
+        <is>
+          <t>CP-SWITCHOVER</t>
+        </is>
+      </c>
+      <c r="B464" s="11" t="inlineStr">
+        <is>
+          <t>SICAM CP-8050 internal</t>
+        </is>
+      </c>
+      <c r="C464" s="11" t="inlineStr">
+        <is>
+          <t>Controller switchover occurred</t>
+        </is>
+      </c>
+      <c r="D464" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="E464" s="11" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="F464" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G464" s="11" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="H464" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I464" s="11" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="J464" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K464" s="11" t="inlineStr">
+        <is>
+          <t>Added rev 1. Logged with time; resets on acknowledgement</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K457"/>
+  <autoFilter ref="A1:K464"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -52919,7 +53521,7 @@
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>Datasheet; CP-8050 system manual; security manual</t>
+          <t>Datasheet; CP-8050 system manual; redundancy description; security manual</t>
         </is>
       </c>
       <c r="H2" s="11" t="inlineStr">
@@ -54610,6 +55212,7 @@
       </c>
       <c r="I43" s="11" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
